--- a/5/search/FY3_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY3_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,34 +492,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="B2" t="n">
-        <v>131.3</v>
+        <v>128.8</v>
       </c>
       <c r="C2" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E2" t="n">
-        <v>6108.86581202595</v>
+        <v>6222.020748156766</v>
       </c>
       <c r="F2" t="n">
-        <v>-402.5404136787938</v>
+        <v>-356.0254264104747</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6129.759250697597</v>
+        <v>6259.742719930974</v>
       </c>
       <c r="I2" t="n">
-        <v>95.96193117073068</v>
+        <v>93.1935545392019</v>
       </c>
       <c r="J2" t="n">
-        <v>629.2439999999999</v>
+        <v>639.975</v>
       </c>
       <c r="K2" t="n">
         <v>3.100000000000001</v>
@@ -530,34 +530,34 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B3" t="n">
-        <v>131.3</v>
+        <v>125.8</v>
       </c>
       <c r="C3" t="n">
-        <v>20.2</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>6185.012305052594</v>
+        <v>6381.673878996922</v>
       </c>
       <c r="F3" t="n">
-        <v>-354.200772057879</v>
+        <v>-284.2492375603674</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6216.152990061446</v>
+        <v>6434.197807299251</v>
       </c>
       <c r="I3" t="n">
-        <v>91.13177125911153</v>
+        <v>89.47793158270127</v>
       </c>
       <c r="J3" t="n">
-        <v>643.356</v>
+        <v>655.9</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -568,34 +568,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90.8</v>
+        <v>93.2</v>
       </c>
       <c r="B4" t="n">
-        <v>131.3</v>
+        <v>129.8</v>
       </c>
       <c r="C4" t="n">
         <v>19.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="E4" t="n">
-        <v>5964.435254996522</v>
+        <v>5859.434751846615</v>
       </c>
       <c r="F4" t="n">
-        <v>-453.0282927930202</v>
+        <v>-485.8063428980699</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>5956.735671026698</v>
+        <v>5826.829410780108</v>
       </c>
       <c r="I4" t="n">
-        <v>98.37795309715068</v>
+        <v>97.38290746062523</v>
       </c>
       <c r="J4" t="n">
-        <v>613.5640000000001</v>
+        <v>600.775</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -606,34 +606,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="B5" t="n">
-        <v>127.3</v>
+        <v>124.8</v>
       </c>
       <c r="C5" t="n">
-        <v>19.8</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="E5" t="n">
-        <v>5824.176017668982</v>
+        <v>6389.061187195883</v>
       </c>
       <c r="F5" t="n">
-        <v>-485.5999087581026</v>
+        <v>-231.685808471565</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>5783.328021773897</v>
+        <v>6432.483194695423</v>
       </c>
       <c r="I5" t="n">
-        <v>98.553647793045</v>
+        <v>77.27782897580499</v>
       </c>
       <c r="J5" t="n">
-        <v>596.3160000000001</v>
+        <v>669.375</v>
       </c>
       <c r="K5" t="n">
         <v>3</v>
@@ -644,34 +644,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="B6" t="n">
-        <v>127.3</v>
+        <v>128.8</v>
       </c>
       <c r="C6" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>5894.450739749404</v>
+        <v>6000</v>
       </c>
       <c r="F6" t="n">
-        <v>-481.6709418226233</v>
+        <v>-424</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>5869.929194438659</v>
+        <v>6000</v>
       </c>
       <c r="I6" t="n">
-        <v>103.395405026666</v>
+        <v>91.20000000000005</v>
       </c>
       <c r="J6" t="n">
-        <v>596.3160000000001</v>
+        <v>621.6</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -682,37 +682,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="B7" t="n">
-        <v>129.3</v>
+        <v>133.8</v>
       </c>
       <c r="C7" t="n">
-        <v>19.8</v>
+        <v>20.6</v>
       </c>
       <c r="D7" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="E7" t="n">
-        <v>6035.74513637346</v>
+        <v>6307.239588461652</v>
       </c>
       <c r="F7" t="n">
-        <v>-440.1095521828192</v>
+        <v>-260.897359776031</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6043.327438028437</v>
+        <v>6344.525946284668</v>
       </c>
       <c r="I7" t="n">
-        <v>102.8975125056735</v>
+        <v>71.51800918318861</v>
       </c>
       <c r="J7" t="n">
-        <v>613.5640000000001</v>
+        <v>669.375</v>
       </c>
       <c r="K7" t="n">
-        <v>2.900000000000002</v>
+        <v>2.900000000000006</v>
       </c>
       <c r="L7" t="n">
         <v>10</v>
@@ -720,37 +720,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="B8" t="n">
-        <v>126.3</v>
+        <v>127.8</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="D8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E8" t="n">
-        <v>6111.066796385957</v>
+        <v>6073.508739834765</v>
       </c>
       <c r="F8" t="n">
-        <v>-350.0265177287979</v>
+        <v>-368.3464423355595</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6129.04903961035</v>
+        <v>6085.998088835818</v>
       </c>
       <c r="I8" t="n">
-        <v>79.01680797225373</v>
+        <v>78.77916212199108</v>
       </c>
       <c r="J8" t="n">
-        <v>643.356</v>
+        <v>639.975</v>
       </c>
       <c r="K8" t="n">
-        <v>2.899999999999999</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L8" t="n">
         <v>10</v>
@@ -758,37 +758,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90.8</v>
+        <v>85.2</v>
       </c>
       <c r="B9" t="n">
-        <v>128.3</v>
+        <v>125.8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.2</v>
+        <v>21.2</v>
       </c>
       <c r="D9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="E9" t="n">
-        <v>5963.814775702251</v>
+        <v>6223.165461053552</v>
       </c>
       <c r="F9" t="n">
-        <v>-408.5926246260465</v>
+        <v>-342.3934040959416</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>5957.007654299704</v>
+        <v>6260.00881547277</v>
       </c>
       <c r="I9" t="n">
-        <v>78.89985192944982</v>
+        <v>96.36240183161522</v>
       </c>
       <c r="J9" t="n">
-        <v>629.2439999999999</v>
+        <v>639.975</v>
       </c>
       <c r="K9" t="n">
-        <v>2.899999999999999</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L9" t="n">
         <v>10</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>92.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="B10" t="n">
-        <v>130.3</v>
+        <v>127.8</v>
       </c>
       <c r="C10" t="n">
-        <v>19.8</v>
+        <v>21.8</v>
       </c>
       <c r="D10" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="E10" t="n">
-        <v>5891.963325917889</v>
+        <v>6387.74182619878</v>
       </c>
       <c r="F10" t="n">
-        <v>-422.3230457147511</v>
+        <v>-241.073549763235</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>5871.229014730413</v>
+        <v>6432.207631955522</v>
       </c>
       <c r="I10" t="n">
-        <v>72.38263238039781</v>
+        <v>75.31709819969683</v>
       </c>
       <c r="J10" t="n">
-        <v>629.2439999999999</v>
+        <v>669.375</v>
       </c>
       <c r="K10" t="n">
-        <v>2.800000000000004</v>
+        <v>2.900000000000002</v>
       </c>
       <c r="L10" t="n">
         <v>10</v>
@@ -834,37 +834,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>86</v>
+        <v>86.8</v>
       </c>
       <c r="B11" t="n">
-        <v>127.3</v>
+        <v>133.8</v>
       </c>
       <c r="C11" t="n">
-        <v>20.6</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>6182.927981617119</v>
+        <v>6149.378347361707</v>
       </c>
       <c r="F11" t="n">
-        <v>-384.0079858796421</v>
+        <v>-328.1725150490183</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>6216.671978226103</v>
+        <v>6171.785099465963</v>
       </c>
       <c r="I11" t="n">
-        <v>98.5536477930454</v>
+        <v>72.60160769362892</v>
       </c>
       <c r="J11" t="n">
-        <v>629.2439999999999</v>
+        <v>655.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.800000000000001</v>
+        <v>2.899999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>10</v>

--- a/5/search/FY3_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY3_Missile1_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,382 +492,382 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>85.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="B2" t="n">
-        <v>128.8</v>
+        <v>131.4</v>
       </c>
       <c r="C2" t="n">
-        <v>20.6</v>
+        <v>23.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="E2" t="n">
-        <v>6222.020748156766</v>
+        <v>6814.680959968327</v>
       </c>
       <c r="F2" t="n">
-        <v>-356.0254264104747</v>
+        <v>19.34186800121824</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>6259.742719930974</v>
+        <v>6831.796106186149</v>
       </c>
       <c r="I2" t="n">
-        <v>93.1935545392019</v>
+        <v>82.77341984998333</v>
       </c>
       <c r="J2" t="n">
-        <v>639.975</v>
+        <v>698.775</v>
       </c>
       <c r="K2" t="n">
-        <v>3.100000000000001</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="B3" t="n">
-        <v>125.8</v>
+        <v>132.6</v>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>23.8</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0.4</v>
       </c>
       <c r="E3" t="n">
-        <v>6381.673878996922</v>
+        <v>6864.582419087074</v>
       </c>
       <c r="F3" t="n">
-        <v>-284.2492375603674</v>
+        <v>35.1401639801652</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
       </c>
       <c r="H3" t="n">
-        <v>6434.197807299251</v>
+        <v>6879.11321604652</v>
       </c>
       <c r="I3" t="n">
-        <v>89.47793158270127</v>
+        <v>86.15092303865518</v>
       </c>
       <c r="J3" t="n">
-        <v>655.9</v>
+        <v>699.216</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>93.2</v>
+        <v>75.7</v>
       </c>
       <c r="B4" t="n">
-        <v>129.8</v>
+        <v>131.4</v>
       </c>
       <c r="C4" t="n">
-        <v>19.4</v>
+        <v>23.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>5859.434751846615</v>
+        <v>6752.971550305027</v>
       </c>
       <c r="F4" t="n">
-        <v>-485.8063428980699</v>
+        <v>-45.97492312078657</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>5826.829410780108</v>
+        <v>6785.427220576796</v>
       </c>
       <c r="I4" t="n">
-        <v>97.38290746062523</v>
+        <v>81.35374398607608</v>
       </c>
       <c r="J4" t="n">
-        <v>600.775</v>
+        <v>695.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="B5" t="n">
-        <v>124.8</v>
+        <v>132.6</v>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="E5" t="n">
-        <v>6389.061187195883</v>
+        <v>6801.395230027551</v>
       </c>
       <c r="F5" t="n">
-        <v>-231.685808471565</v>
+        <v>-29.89723617362279</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6432.483194695423</v>
+        <v>6832.483838088965</v>
       </c>
       <c r="I5" t="n">
-        <v>77.27782897580499</v>
+        <v>85.32226759550375</v>
       </c>
       <c r="J5" t="n">
-        <v>669.375</v>
+        <v>696.0310000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="B6" t="n">
-        <v>128.8</v>
+        <v>131</v>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>23.6</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="E6" t="n">
-        <v>6000</v>
+        <v>6846.972320509524</v>
       </c>
       <c r="F6" t="n">
-        <v>-424</v>
+        <v>-26.68056739765825</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>6000</v>
+        <v>6879.272112393362</v>
       </c>
       <c r="I6" t="n">
-        <v>91.20000000000005</v>
+        <v>86.70873299819358</v>
       </c>
       <c r="J6" t="n">
-        <v>621.6</v>
+        <v>696.0310000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.200000000000003</v>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>83.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="B7" t="n">
-        <v>133.8</v>
+        <v>131.4</v>
       </c>
       <c r="C7" t="n">
-        <v>20.6</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="E7" t="n">
-        <v>6307.239588461652</v>
+        <v>6863.957792068455</v>
       </c>
       <c r="F7" t="n">
-        <v>-260.897359776031</v>
+        <v>32.94739379439307</v>
       </c>
       <c r="G7" t="n">
         <v>700</v>
       </c>
       <c r="H7" t="n">
-        <v>6344.525946284668</v>
+        <v>6878.357088602929</v>
       </c>
       <c r="I7" t="n">
-        <v>71.51800918318861</v>
+        <v>83.49651702429944</v>
       </c>
       <c r="J7" t="n">
-        <v>669.375</v>
+        <v>699.216</v>
       </c>
       <c r="K7" t="n">
-        <v>2.900000000000006</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>127.8</v>
+        <v>132.6</v>
       </c>
       <c r="C8" t="n">
-        <v>20.6</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>3.5</v>
+        <v>0.2</v>
       </c>
       <c r="E8" t="n">
-        <v>6073.508739834765</v>
+        <v>6871.847817566797</v>
       </c>
       <c r="F8" t="n">
-        <v>-368.3464423355595</v>
+        <v>60.64554350941034</v>
       </c>
       <c r="G8" t="n">
         <v>700</v>
       </c>
       <c r="H8" t="n">
-        <v>6085.998088835818</v>
+        <v>6879.11321604652</v>
       </c>
       <c r="I8" t="n">
-        <v>78.77916212199108</v>
+        <v>86.15092303865534</v>
       </c>
       <c r="J8" t="n">
-        <v>639.975</v>
+        <v>699.804</v>
       </c>
       <c r="K8" t="n">
-        <v>2.900000000000002</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>85.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="B9" t="n">
-        <v>125.8</v>
+        <v>132.6</v>
       </c>
       <c r="C9" t="n">
-        <v>21.2</v>
+        <v>23.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>6223.165461053552</v>
+        <v>6850.051622127628</v>
       </c>
       <c r="F9" t="n">
-        <v>-342.3934040959416</v>
+        <v>-15.8705950783251</v>
       </c>
       <c r="G9" t="n">
         <v>700</v>
       </c>
       <c r="H9" t="n">
-        <v>6260.00881547277</v>
+        <v>6879.11321604652</v>
       </c>
       <c r="I9" t="n">
-        <v>96.36240183161522</v>
+        <v>86.15092303865534</v>
       </c>
       <c r="J9" t="n">
-        <v>639.975</v>
+        <v>696.864</v>
       </c>
       <c r="K9" t="n">
-        <v>2.900000000000002</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="B10" t="n">
-        <v>127.8</v>
+        <v>131.4</v>
       </c>
       <c r="C10" t="n">
-        <v>21.8</v>
+        <v>24.2</v>
       </c>
       <c r="D10" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="E10" t="n">
-        <v>6387.74182619878</v>
+        <v>6871.157440335693</v>
       </c>
       <c r="F10" t="n">
-        <v>-241.073549763235</v>
+        <v>58.22195540934581</v>
       </c>
       <c r="G10" t="n">
         <v>700</v>
       </c>
       <c r="H10" t="n">
-        <v>6432.207631955522</v>
+        <v>6878.35708860293</v>
       </c>
       <c r="I10" t="n">
-        <v>75.31709819969683</v>
+        <v>83.496517024299</v>
       </c>
       <c r="J10" t="n">
-        <v>669.375</v>
+        <v>699.804</v>
       </c>
       <c r="K10" t="n">
-        <v>2.900000000000002</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>86.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>133.8</v>
+        <v>132</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>24.2</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0.1</v>
       </c>
       <c r="E11" t="n">
-        <v>6149.378347361707</v>
+        <v>6875.135328191107</v>
       </c>
       <c r="F11" t="n">
-        <v>-328.1725150490183</v>
+        <v>72.18643922400042</v>
       </c>
       <c r="G11" t="n">
         <v>700</v>
       </c>
       <c r="H11" t="n">
-        <v>6171.785099465963</v>
+        <v>6878.751589877847</v>
       </c>
       <c r="I11" t="n">
-        <v>72.60160769362892</v>
+        <v>84.88142451005019</v>
       </c>
       <c r="J11" t="n">
-        <v>655.9</v>
+        <v>699.951</v>
       </c>
       <c r="K11" t="n">
-        <v>2.899999999999999</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
